--- a/data/trans_orig/P44C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P44C-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2012</t>
+          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2012 (tasa de respuesta: 98,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,62 +767,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1890</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4078</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4879</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>56,05%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>890</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>10892</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>60,43%</t>
         </is>
       </c>
     </row>
@@ -1301,97 +1301,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2289</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5123</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>25,1%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>1117</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5563</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>5808</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>27,25%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>5918</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13581</t>
+          <t>13678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13200</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23908</t>
+          <t>23598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,0%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30112</t>
+          <t>30462</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -1870,97 +1870,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1913</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1931</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>18508</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10971</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>11469</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>46,62%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10945</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17361</t>
+          <t>17280</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,24%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -3008,97 +3008,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1664</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>57,74%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>984</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>76,52%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>989</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -3577,97 +3577,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1662</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1846</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8196</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>12487</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13097</t>
+          <t>13437</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11558</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>18324</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,74%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10341</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>20792</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15939</t>
+          <t>15949</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -4715,97 +4715,97 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>2129</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>17152</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22188</t>
+          <t>22307</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>18258</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>31912</t>
+          <t>31655</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>75,55%</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>973</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>23660</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>18942</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>38664</t>
+          <t>39232</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>27821</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>47349</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>51876</t>
+          <t>51024</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>80343</t>
+          <t>80301</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>50909</t>
+          <t>51277</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>73194</t>
+          <t>74781</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>34841</t>
+          <t>35205</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>55452</t>
+          <t>55268</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>90228</t>
+          <t>91409</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>121839</t>
+          <t>123486</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,71%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>24318</t>
+          <t>23998</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>31417</t>
+          <t>31350</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>27773</t>
+          <t>27682</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>50774</t>
+          <t>50530</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2016</t>
+          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2016 (tasa de respuesta: 96,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11265</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15107</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9819</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>22313</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>56,62%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -6658,97 +6658,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1758</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1778</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1890</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6771,12 +6771,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,31%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,39%</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>10184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18448</t>
+          <t>17764</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24031</t>
+          <t>24794</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35088</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>793</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>12599</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>10945</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20212</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,5%</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16577</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15494</t>
+          <t>16085</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29093</t>
+          <t>29469</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>65,41%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -8400,62 +8400,62 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1446</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>3997</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>4708</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -8478,97 +8478,97 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1052</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3097</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>26,38%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>77,65%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1052</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3989</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>26,38%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4125</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>15,12%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3872</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>15,12%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>59,26%</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>892</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -8704,97 +8704,97 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>1446</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>1618</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8934,97 +8934,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1774</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1786</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10521</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>59,1%</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7865</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13586</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>
@@ -9273,12 +9273,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,53%</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8221</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>910</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13732</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>9369</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24145</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>28718</t>
+          <t>28555</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>19313</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>27001</t>
+          <t>27557</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>45519</t>
+          <t>45634</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,74%</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>22028</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -10077,7 +10077,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -10185,12 +10185,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>10540</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>24503</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>17762</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>30204</t>
+          <t>30706</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -10411,12 +10411,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9437</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>15329</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10496,12 +10496,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -10641,12 +10641,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10656,12 +10656,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>28426</t>
+          <t>27575</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>22274</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>40448</t>
+          <t>41378</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>24593</t>
+          <t>24306</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>46174</t>
+          <t>45713</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>51179</t>
+          <t>51092</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>79893</t>
+          <t>80865</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>76343</t>
+          <t>74838</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>100789</t>
+          <t>100450</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>47601</t>
+          <t>48465</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>70884</t>
+          <t>70419</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10937,12 +10937,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>131392</t>
+          <t>131283</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>164940</t>
+          <t>164151</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10952,12 +10952,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -10980,12 +10980,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>22313</t>
+          <t>20940</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>41449</t>
+          <t>42226</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>25559</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>33488</t>
+          <t>33146</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>59805</t>
+          <t>59107</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11065,12 +11065,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2023</t>
+          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2023 (tasa de respuesta: 96,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11446,12 +11446,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>502</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -11559,12 +11559,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25618</t>
+          <t>25217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>40203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11574,12 +11574,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14741</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22940</t>
+          <t>22766</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43507</t>
+          <t>43524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29309</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45265</t>
+          <t>45776</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>19288</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43815</t>
+          <t>44074</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61541</t>
+          <t>61378</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11757,12 +11757,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,29%</t>
         </is>
       </c>
     </row>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11820,62 +11820,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>899</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4469</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>927</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4838</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -12015,12 +12015,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12050,12 +12050,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12085,12 +12085,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -12128,12 +12128,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22096</t>
+          <t>22376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14045</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32463</t>
+          <t>32435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12213,12 +12213,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -12241,12 +12241,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17394</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32888</t>
+          <t>32966</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12256,12 +12256,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13667</t>
+          <t>13760</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25404</t>
+          <t>24392</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43397</t>
+          <t>43293</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -12354,12 +12354,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27744</t>
+          <t>27540</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22377</t>
+          <t>22004</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12404,12 +12404,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28278</t>
+          <t>28565</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46259</t>
+          <t>46767</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12439,12 +12439,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12669,12 +12669,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21181</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33521</t>
+          <t>34241</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>27994</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12747,12 +12747,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>42292</t>
+          <t>41799</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>57995</t>
+          <t>58622</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12782,12 +12782,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>52,08%</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>23328</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>12510</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22164</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26676</t>
+          <t>26756</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41534</t>
+          <t>42333</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -12923,12 +12923,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17735</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12938,12 +12938,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17192</t>
+          <t>16956</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12973,12 +12973,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>17459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30763</t>
+          <t>31344</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13008,12 +13008,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -13153,12 +13153,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10052</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13238,12 +13238,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -13266,12 +13266,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27814</t>
+          <t>29016</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21086</t>
+          <t>21522</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31481</t>
+          <t>31615</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40437</t>
+          <t>40710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57367</t>
+          <t>56816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -13379,12 +13379,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26135</t>
+          <t>26246</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29492</t>
+          <t>29677</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45403</t>
+          <t>45456</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,97%</t>
         </is>
       </c>
     </row>
@@ -13492,12 +13492,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13507,12 +13507,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8747</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13577,12 +13577,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -13722,97 +13722,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>980</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13840,7 +13840,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>2287</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -13948,12 +13948,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13983,12 +13983,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12598</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14018,12 +14018,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16492</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22474</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14033,12 +14033,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -14061,12 +14061,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14076,12 +14076,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>718</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14111,12 +14111,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14131,12 +14131,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14146,12 +14146,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -14291,12 +14291,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>401</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>398</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -14404,12 +14404,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14474,12 +14474,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14489,12 +14489,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -14517,12 +14517,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13517</t>
+          <t>13802</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22910</t>
+          <t>22890</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14552,12 +14552,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14587,12 +14587,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>21165</t>
+          <t>21277</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>33183</t>
+          <t>33162</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -14630,12 +14630,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19885</t>
+          <t>19469</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14665,12 +14665,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17176</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>22015</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>33801</t>
+          <t>33870</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -14860,12 +14860,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14930,12 +14930,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15246</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14945,12 +14945,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -14973,12 +14973,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>36264</t>
+          <t>34849</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15008,12 +15008,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>24447</t>
+          <t>24225</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>38220</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15043,12 +15043,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>47171</t>
+          <t>47421</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>69193</t>
+          <t>69540</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15058,12 +15058,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -15086,12 +15086,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>37115</t>
+          <t>36409</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>55972</t>
+          <t>55280</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>47518</t>
+          <t>47817</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>63135</t>
+          <t>63100</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>88110</t>
+          <t>90647</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>113183</t>
+          <t>113785</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,57%</t>
         </is>
       </c>
     </row>
@@ -15199,12 +15199,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11307</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>25784</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>37175</t>
+          <t>37711</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -15429,97 +15429,97 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>1199</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>3815</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3735</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>1199</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="S39" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>4141</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>4665</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>1199</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>4554</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15577,12 +15577,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>21850</t>
+          <t>20688</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -15655,12 +15655,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>236720</t>
+          <t>236574</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>360009</t>
+          <t>360239</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15670,12 +15670,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15690,12 +15690,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>90354</t>
+          <t>89226</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>104158</t>
+          <t>103756</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>346705</t>
+          <t>345055</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>479333</t>
+          <t>474535</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -15768,12 +15768,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8805</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>120335</t>
+          <t>120839</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15803,12 +15803,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>19535</t>
+          <t>19982</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>32677</t>
+          <t>32750</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>17332</t>
+          <t>21019</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>131672</t>
+          <t>133901</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -15998,12 +15998,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>29936</t>
+          <t>30049</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>22684</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>47437</t>
+          <t>46826</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -16111,12 +16111,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>58533</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>206973</t>
+          <t>206265</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16126,12 +16126,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16146,12 +16146,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>109448</t>
+          <t>109523</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>137542</t>
+          <t>136271</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>132329</t>
+          <t>144870</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>328199</t>
+          <t>331605</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>361880</t>
+          <t>364625</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>657643</t>
+          <t>640739</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>218943</t>
+          <t>219764</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>250191</t>
+          <t>250484</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>601049</t>
+          <t>598928</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>963009</t>
+          <t>952101</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,14%</t>
         </is>
       </c>
     </row>
@@ -16337,12 +16337,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>43719</t>
+          <t>47802</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>170456</t>
+          <t>169570</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16352,12 +16352,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16372,12 +16372,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>73611</t>
+          <t>74463</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>99064</t>
+          <t>99139</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16387,12 +16387,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16407,12 +16407,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>105672</t>
+          <t>100041</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>253621</t>
+          <t>253406</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P44C-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>58,57%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>821</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,49%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>937</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>64,55%</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13678</t>
+          <t>13496</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23598</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>56,07%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>19881</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30462</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,84%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11344</t>
+          <t>11142</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18508</t>
+          <t>18585</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,48%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>10939</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11245</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10945</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17280</t>
+          <t>17069</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>944</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,64%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>57,3%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,91%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12487</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11558</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,99%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10496</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,04%</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15949</t>
+          <t>16530</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>14024</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10690</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22307</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>12779</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>18258</t>
+          <t>18449</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>31655</t>
+          <t>31894</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>76,12%</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>14210</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>23660</t>
+          <t>23671</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>39232</t>
+          <t>39901</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>26793</t>
+          <t>27142</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>46565</t>
+          <t>46246</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>51024</t>
+          <t>50903</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>80301</t>
+          <t>79550</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>51277</t>
+          <t>51999</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>74781</t>
+          <t>74225</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>34549</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>55268</t>
+          <t>56659</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>91409</t>
+          <t>92086</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>123486</t>
+          <t>124029</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,96%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>23487</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>13883</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>31350</t>
+          <t>31528</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>27682</t>
+          <t>26805</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>50530</t>
+          <t>50495</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11920</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>14742</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22313</t>
+          <t>22230</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,41%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11337</t>
+          <t>11382</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18001</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>10453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>12832</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>923</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>8317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>10418</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>18188</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>11349</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18120</t>
+          <t>18166</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24794</t>
+          <t>24518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35265</t>
+          <t>35071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,04%</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>7130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9139</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>814</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12599</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10945</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20500</t>
+          <t>19828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>17041</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15555</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29469</t>
+          <t>28641</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>63,57%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11207</t>
+          <t>11543</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>58,45%</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>10857</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>71,9%</t>
         </is>
       </c>
     </row>
@@ -9273,12 +9273,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>48,86%</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>892</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>12775</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>25207</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>36,31%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>15902</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>28555</t>
+          <t>28956</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19313</t>
+          <t>19247</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>27557</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>45634</t>
+          <t>44952</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>64,76%</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14506</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>12005</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>22028</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -10077,7 +10077,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>24503</t>
+          <t>24446</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>17397</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>30706</t>
+          <t>30049</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>75,36%</t>
         </is>
       </c>
     </row>
@@ -10411,12 +10411,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>15329</t>
+          <t>14970</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10496,12 +10496,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -10641,12 +10641,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>20610</t>
+          <t>20204</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10656,12 +10656,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>27917</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>20249</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>39915</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>24306</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>45713</t>
+          <t>45580</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>51092</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>80865</t>
+          <t>79629</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>74838</t>
+          <t>75236</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>100450</t>
+          <t>100180</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>48465</t>
+          <t>47841</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>70419</t>
+          <t>70864</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10937,12 +10937,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>131283</t>
+          <t>130394</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>164151</t>
+          <t>163698</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10952,12 +10952,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -10980,12 +10980,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>21694</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>42057</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>25559</t>
+          <t>25306</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>33146</t>
+          <t>35208</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>59107</t>
+          <t>61166</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11065,12 +11065,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -11441,32 +11441,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11476,32 +11476,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11511,32 +11511,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -11554,32 +11554,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32985</t>
+          <t>32121</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25217</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40203</t>
+          <t>39758</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11589,32 +11589,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18968</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>15765</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22766</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11624,32 +11624,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>51954</t>
+          <t>51732</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43524</t>
+          <t>43444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60743</t>
+          <t>60317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>54,73%</t>
         </is>
       </c>
     </row>
@@ -11667,32 +11667,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37795</t>
+          <t>38354</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30961</t>
+          <t>30466</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45776</t>
+          <t>45960</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11702,32 +11702,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11237</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>19507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11737,32 +11737,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>52932</t>
+          <t>53921</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44074</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61378</t>
+          <t>62212</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,45%</t>
         </is>
       </c>
     </row>
@@ -11780,7 +11780,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>839</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -11790,12 +11790,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>839</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -11860,12 +11860,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -11893,17 +11893,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>73367</t>
+          <t>73539</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73367</t>
+          <t>73539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73367</t>
+          <t>73539</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11928,17 +11928,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11963,17 +11963,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>109046</t>
+          <t>110209</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109046</t>
+          <t>110209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109046</t>
+          <t>110209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12010,32 +12010,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12045,32 +12045,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12080,32 +12080,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>11743</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -12123,32 +12123,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>22411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12158,32 +12158,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12193,32 +12193,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>24020</t>
+          <t>25321</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16470</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32435</t>
+          <t>33904</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -12236,32 +12236,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25251</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>34684</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12271,32 +12271,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13760</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12306,32 +12306,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>34238</t>
+          <t>35802</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24392</t>
+          <t>27443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43293</t>
+          <t>46496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -12349,32 +12349,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19793</t>
+          <t>20840</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12615</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27540</t>
+          <t>29244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12384,32 +12384,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17281</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22004</t>
+          <t>23497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12419,32 +12419,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>37074</t>
+          <t>39186</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>30134</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46767</t>
+          <t>48782</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -12462,17 +12462,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62724</t>
+          <t>65162</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62724</t>
+          <t>65162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62724</t>
+          <t>65162</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12497,17 +12497,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38238</t>
+          <t>40888</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38238</t>
+          <t>40888</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38238</t>
+          <t>40888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12532,17 +12532,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>100963</t>
+          <t>106050</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100963</t>
+          <t>106050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100963</t>
+          <t>106050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>563</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -12589,12 +12589,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12614,32 +12614,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12649,32 +12649,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -12692,32 +12692,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27246</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21619</t>
+          <t>20515</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34241</t>
+          <t>32861</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12727,32 +12727,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22749</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17812</t>
+          <t>18659</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27994</t>
+          <t>29280</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12762,32 +12762,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>49995</t>
+          <t>50149</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>41799</t>
+          <t>42144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>58622</t>
+          <t>58362</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -12805,67 +12805,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17255</t>
+          <t>17016</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>22634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>30,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>22,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>17378</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>12901</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>23079</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>30,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>21,08%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>41,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17123</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>12510</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>22276</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12875,32 +12875,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>34378</t>
+          <t>34394</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26756</t>
+          <t>27501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42333</t>
+          <t>42314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -12918,32 +12918,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11737</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>17593</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12953,32 +12953,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16956</t>
+          <t>17094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12988,32 +12988,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>23942</t>
+          <t>24059</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31344</t>
+          <t>31207</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -13031,17 +13031,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>56800</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56800</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56800</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13066,17 +13066,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>55754</t>
+          <t>57202</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55754</t>
+          <t>57202</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55754</t>
+          <t>57202</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13101,17 +13101,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>112555</t>
+          <t>112844</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>112555</t>
+          <t>112844</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>112555</t>
+          <t>112844</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13148,32 +13148,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>12052</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13183,32 +13183,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13218,32 +13218,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -13261,32 +13261,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>22516</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29016</t>
+          <t>30112</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13296,32 +13296,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>26235</t>
+          <t>27801</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21522</t>
+          <t>22254</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31615</t>
+          <t>33819</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13331,32 +13331,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>48751</t>
+          <t>51140</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40710</t>
+          <t>41943</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56816</t>
+          <t>60632</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -13374,32 +13374,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>18279</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>25034</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13409,32 +13409,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21111</t>
+          <t>23572</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16244</t>
+          <t>18319</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26246</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13444,32 +13444,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>36984</t>
+          <t>41851</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29677</t>
+          <t>33874</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45456</t>
+          <t>50585</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -13487,32 +13487,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13522,32 +13522,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13557,32 +13557,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14905</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -13600,17 +13600,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>47939</t>
+          <t>54208</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47939</t>
+          <t>54208</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47939</t>
+          <t>54208</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>55438</t>
+          <t>60347</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>55438</t>
+          <t>60347</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55438</t>
+          <t>60347</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13670,17 +13670,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>103377</t>
+          <t>114555</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>103377</t>
+          <t>114555</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103377</t>
+          <t>114555</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>691</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -13840,12 +13840,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>373</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -13943,32 +13943,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13978,32 +13978,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14013,32 +14013,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>20093</t>
+          <t>21225</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>17934</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22682</t>
+          <t>24039</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -14056,32 +14056,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14091,32 +14091,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>729</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14126,32 +14126,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8317</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -14169,17 +14169,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14204,17 +14204,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>27409</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>27409</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>27409</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14286,32 +14286,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>419</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14356,32 +14356,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>419</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -14399,32 +14399,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2391</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14434,32 +14434,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14469,32 +14469,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>19467</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -14512,32 +14512,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>17556</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13802</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22890</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14547,32 +14547,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14582,32 +14582,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>26083</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>21277</t>
+          <t>20406</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>33162</t>
+          <t>32786</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -14625,32 +14625,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>14323</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19469</t>
+          <t>18821</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14660,32 +14660,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17383</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14695,32 +14695,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>27678</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>21395</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>33870</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -14738,17 +14738,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>38935</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>38935</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>38935</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14773,17 +14773,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -14808,17 +14808,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>69486</t>
+          <t>68866</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>69486</t>
+          <t>68866</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>69486</t>
+          <t>68866</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -14855,32 +14855,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>12036</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14890,32 +14890,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14925,32 +14925,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14941</t>
+          <t>17120</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -14968,32 +14968,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>26407</t>
+          <t>28327</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>34849</t>
+          <t>38807</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15003,32 +15003,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>31206</t>
+          <t>37028</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>24225</t>
+          <t>29114</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15038,32 +15038,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>57613</t>
+          <t>65355</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>54352</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>69540</t>
+          <t>79075</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -15081,32 +15081,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>46117</t>
+          <t>54256</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>44099</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>55280</t>
+          <t>64771</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15116,22 +15116,22 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>55850</t>
+          <t>65460</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>47817</t>
+          <t>56736</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>63100</t>
+          <t>73605</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15151,32 +15151,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>101967</t>
+          <t>119715</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>90647</t>
+          <t>105749</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>113785</t>
+          <t>132745</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,59%</t>
         </is>
       </c>
     </row>
@@ -15194,32 +15194,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>17906</t>
+          <t>21288</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>25425</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15229,32 +15229,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>16658</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15264,32 +15264,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>28895</t>
+          <t>34927</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>25868</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>37711</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -15307,17 +15307,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>96263</t>
+          <t>110218</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>96263</t>
+          <t>110218</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>96263</t>
+          <t>110218</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -15342,17 +15342,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>101377</t>
+          <t>120278</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>101377</t>
+          <t>120278</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>101377</t>
+          <t>120278</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -15377,17 +15377,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>197640</t>
+          <t>230495</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>197640</t>
+          <t>230495</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>197640</t>
+          <t>230495</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -15469,12 +15469,12 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -15504,12 +15504,12 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
@@ -15519,7 +15519,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -15537,32 +15537,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15572,32 +15572,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15607,32 +15607,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>20688</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -15650,32 +15650,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>327338</t>
+          <t>93091</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>236574</t>
+          <t>82849</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>360239</t>
+          <t>102247</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15685,32 +15685,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>97003</t>
+          <t>111262</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>89226</t>
+          <t>102457</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>103756</t>
+          <t>119439</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15720,32 +15720,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>424341</t>
+          <t>204354</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>345055</t>
+          <t>190873</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>474535</t>
+          <t>216411</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>75,15%</t>
         </is>
       </c>
     </row>
@@ -15763,32 +15763,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>38387</t>
+          <t>42351</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>32562</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>120839</t>
+          <t>51824</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15798,32 +15798,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>26066</t>
+          <t>29424</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>22197</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>32750</t>
+          <t>37772</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15833,32 +15833,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>64453</t>
+          <t>71774</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>21019</t>
+          <t>60274</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>133901</t>
+          <t>84857</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -15876,17 +15876,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>369897</t>
+          <t>140041</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>369897</t>
+          <t>140041</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>369897</t>
+          <t>140041</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15911,17 +15911,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>129556</t>
+          <t>147948</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>129556</t>
+          <t>147948</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>129556</t>
+          <t>147948</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15946,17 +15946,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>499453</t>
+          <t>287989</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>499453</t>
+          <t>287989</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>499453</t>
+          <t>287989</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15993,32 +15993,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>30049</t>
+          <t>29587</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16028,32 +16028,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>22188</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16063,32 +16063,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>33449</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>46826</t>
+          <t>47606</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -16106,32 +16106,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>133609</t>
+          <t>135435</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>58533</t>
+          <t>116336</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>206265</t>
+          <t>154372</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16141,32 +16141,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>123117</t>
+          <t>133678</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>109523</t>
+          <t>119217</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>136271</t>
+          <t>150204</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16176,32 +16176,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>256725</t>
+          <t>269113</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>144870</t>
+          <t>245856</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>331605</t>
+          <t>293577</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -16219,32 +16219,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>496330</t>
+          <t>273817</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>364625</t>
+          <t>252038</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>640739</t>
+          <t>294976</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16254,32 +16254,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>235084</t>
+          <t>263528</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>219764</t>
+          <t>246515</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>250484</t>
+          <t>279340</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16289,32 +16289,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>731413</t>
+          <t>537345</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>598928</t>
+          <t>510021</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>952101</t>
+          <t>564019</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>53,29%</t>
         </is>
       </c>
     </row>
@@ -16332,32 +16332,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>110704</t>
+          <t>120765</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>47802</t>
+          <t>104858</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>169570</t>
+          <t>139404</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16367,32 +16367,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>94242</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>74463</t>
+          <t>80856</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>99139</t>
+          <t>107921</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16402,32 +16402,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>196903</t>
+          <t>215007</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>100041</t>
+          <t>193691</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>253406</t>
+          <t>237797</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -16445,17 +16445,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>758288</t>
+          <t>549646</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>758288</t>
+          <t>549646</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>758288</t>
+          <t>549646</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -16480,17 +16480,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>460203</t>
+          <t>508772</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>460203</t>
+          <t>508772</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>460203</t>
+          <t>508772</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -16515,17 +16515,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1218491</t>
+          <t>1058418</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1218491</t>
+          <t>1058418</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1218491</t>
+          <t>1058418</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
